--- a/tasklist/centauri.xlsx
+++ b/tasklist/centauri.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="253">
   <si>
     <t xml:space="preserve">Task ID</t>
   </si>
@@ -401,7 +401,13 @@
     <t xml:space="preserve"> 真空シール設計（Oリング/メタルシール）</t>
   </si>
   <si>
+    <t>+maxima</t>
+  </si>
+  <si>
     <t xml:space="preserve"> アウトガス量と漏れ率の計算</t>
+  </si>
+  <si>
+    <t>26.05.28</t>
   </si>
   <si>
     <t>C109</t>
@@ -833,17 +839,17 @@
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1414,7 +1420,7 @@
       <c r="F6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1437,14 +1443,14 @@
       <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5" t="s">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="1" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1600,7 +1606,7 @@
       <c r="D18" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="1" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1650,82 +1656,82 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="5" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="5" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7"/>
+      <c r="A31" s="5"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="5" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="5" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="5" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7"/>
+      <c r="A35" s="5"/>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="5" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7"/>
+      <c r="A37" s="5"/>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="5" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1774,7 +1780,7 @@
       <c r="D2" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="1" t="s">
         <v>104</v>
       </c>
     </row>
@@ -1887,28 +1893,28 @@
       <c r="B9" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>102</v>
+      <c r="C9" s="6" t="s">
+        <v>126</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>108</v>
+        <v>127</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="10" ht="57">
       <c r="A10" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>102</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>108</v>
@@ -1916,16 +1922,16 @@
     </row>
     <row r="11" ht="71.25">
       <c r="A11" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>102</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>108</v>
@@ -1948,10 +1954,10 @@
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" ht="14.25">
@@ -1959,7 +1965,7 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" ht="14.25">
@@ -1967,7 +1973,7 @@
         <v>7.0999999999999996</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" ht="14.25">
@@ -1975,7 +1981,7 @@
         <v>7.2000000000000002</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" ht="14.25">
@@ -1983,7 +1989,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" ht="14.25">
@@ -1991,7 +1997,7 @@
         <v>8.0999999999999996</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" ht="14.25">
@@ -1999,7 +2005,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" ht="14.25">
@@ -2007,7 +2013,7 @@
         <v>9.0999999999999996</v>
       </c>
       <c r="B8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" ht="14.25">
@@ -2015,7 +2021,7 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" ht="14.25">
@@ -2023,7 +2029,7 @@
         <v>10.1</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" ht="14.25">
@@ -2031,7 +2037,7 @@
         <v>10.199999999999999</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" ht="14.25">
@@ -2039,7 +2045,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" ht="14.25">
@@ -2047,7 +2053,7 @@
         <v>11.1</v>
       </c>
       <c r="B13" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" ht="14.25">
@@ -2055,7 +2061,7 @@
         <v>11.199999999999999</v>
       </c>
       <c r="B14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" ht="14.25">
@@ -2063,7 +2069,7 @@
         <v>11.300000000000001</v>
       </c>
       <c r="B15" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" ht="14.25">
@@ -2071,7 +2077,7 @@
         <v>11.4</v>
       </c>
       <c r="B16" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" ht="14.25">
@@ -2079,7 +2085,7 @@
         <v>11.5</v>
       </c>
       <c r="B17" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" ht="14.25">
@@ -2087,7 +2093,7 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" ht="14.25">
@@ -2095,7 +2101,7 @@
         <v>12.1</v>
       </c>
       <c r="B19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2121,481 +2127,481 @@
         <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" ht="71.25">
       <c r="A2" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F2" s="11">
         <v>0.84999999999999998</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" ht="42.75">
       <c r="A3" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F3" s="11">
         <v>0.62</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" ht="42.75">
       <c r="A4" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F4" s="11">
         <v>0.45000000000000001</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" ht="42.75">
       <c r="A5" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F5" s="11">
         <v>0.12</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" ht="42.75">
       <c r="A6" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F6" s="11">
         <v>0.34999999999999998</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" ht="42.75">
       <c r="A7" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F7" s="11">
         <v>0.55000000000000004</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" ht="57">
       <c r="A8" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F8" s="11">
         <v>0.29999999999999999</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="7" t="s">
-        <v>215</v>
+      <c r="A10" s="5" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="7"/>
+      <c r="A11" s="5"/>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="7" t="s">
-        <v>216</v>
+      <c r="A12" s="5" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="7" t="s">
-        <v>217</v>
+      <c r="A13" s="5" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="14" ht="14.25">
-      <c r="A14" s="7" t="s">
-        <v>218</v>
+      <c r="A14" s="5" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" s="7" t="s">
-        <v>219</v>
+      <c r="A15" s="5" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="16" ht="14.25">
-      <c r="A16" s="7"/>
+      <c r="A16" s="5"/>
     </row>
     <row r="17" ht="14.25">
-      <c r="A17" s="7" t="s">
-        <v>220</v>
+      <c r="A17" s="5" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="18" ht="14.25">
-      <c r="A18" s="7" t="s">
-        <v>221</v>
+      <c r="A18" s="5" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="19" ht="14.25">
-      <c r="A19" s="7" t="s">
-        <v>222</v>
+      <c r="A19" s="5" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="20" ht="14.25">
-      <c r="A20" s="7" t="s">
-        <v>223</v>
+      <c r="A20" s="5" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="21" ht="14.25">
-      <c r="A21" s="7"/>
+      <c r="A21" s="5"/>
     </row>
     <row r="22" ht="14.25">
-      <c r="A22" s="7" t="s">
-        <v>224</v>
+      <c r="A22" s="5" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" s="7" t="s">
-        <v>225</v>
+      <c r="A23" s="5" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="24" ht="14.25">
-      <c r="A24" s="7" t="s">
-        <v>226</v>
+      <c r="A24" s="5" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="25" ht="14.25">
-      <c r="A25" s="7" t="s">
-        <v>227</v>
+      <c r="A25" s="5" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="26" ht="14.25">
-      <c r="A26" s="7"/>
+      <c r="A26" s="5"/>
     </row>
     <row r="27" ht="14.25">
-      <c r="A27" s="7" t="s">
-        <v>228</v>
+      <c r="A27" s="5" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="28" ht="14.25">
-      <c r="A28" s="7"/>
+      <c r="A28" s="5"/>
     </row>
     <row r="29" ht="14.25">
-      <c r="A29" s="7" t="s">
-        <v>229</v>
+      <c r="A29" s="5" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="30" ht="14.25">
-      <c r="A30" s="7"/>
+      <c r="A30" s="5"/>
     </row>
     <row r="31" ht="14.25">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25">
+      <c r="A32" s="5"/>
+    </row>
+    <row r="33" ht="14.25">
+      <c r="A33" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25">
+      <c r="A34" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25">
+      <c r="A35" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25">
+      <c r="A36" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25">
+      <c r="A37" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25">
+      <c r="A38" s="5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25">
+      <c r="A39" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25">
+      <c r="A40" s="5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25">
+      <c r="A41" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25">
+      <c r="A42" s="5"/>
+    </row>
+    <row r="43" ht="14.25">
+      <c r="A43" s="5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25">
+      <c r="A44" s="5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25">
+      <c r="A45" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="46" ht="14.25">
+      <c r="A46" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25">
+      <c r="A47" s="5" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="48" ht="14.25">
+      <c r="A48" s="5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="49" ht="14.25">
+      <c r="A49" s="5"/>
+    </row>
+    <row r="50" ht="14.25">
+      <c r="A50" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="51" ht="14.25">
+      <c r="A51" s="5"/>
+    </row>
+    <row r="52" ht="14.25">
+      <c r="A52" s="5" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="32" ht="14.25">
-      <c r="A32" s="7"/>
-    </row>
-    <row r="33" ht="14.25">
-      <c r="A33" s="7" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="34" ht="14.25">
-      <c r="A34" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="35" ht="14.25">
-      <c r="A35" s="7" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="36" ht="14.25">
-      <c r="A36" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25">
-      <c r="A37" s="7" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="38" ht="14.25">
-      <c r="A38" s="7" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="39" ht="14.25">
-      <c r="A39" s="7" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="40" ht="14.25">
-      <c r="A40" s="7" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="41" ht="14.25">
-      <c r="A41" s="7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="42" ht="14.25">
-      <c r="A42" s="7"/>
-    </row>
-    <row r="43" ht="14.25">
-      <c r="A43" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="44" ht="14.25">
-      <c r="A44" s="7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="45" ht="14.25">
-      <c r="A45" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="46" ht="14.25">
-      <c r="A46" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="47" ht="14.25">
-      <c r="A47" s="7" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="48" ht="14.25">
-      <c r="A48" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="49" ht="14.25">
-      <c r="A49" s="7"/>
-    </row>
-    <row r="50" ht="14.25">
-      <c r="A50" s="7" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="51" ht="14.25">
-      <c r="A51" s="7"/>
-    </row>
-    <row r="52" ht="14.25">
-      <c r="A52" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
     <row r="53" ht="14.25">
-      <c r="A53" s="7"/>
+      <c r="A53" s="5"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="A54" s="7" t="s">
-        <v>246</v>
+      <c r="A54" s="5" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="55" ht="14.25">
-      <c r="A55" s="7"/>
+      <c r="A55" s="5"/>
     </row>
     <row r="56" ht="14.25">
-      <c r="A56" s="7" t="s">
-        <v>247</v>
+      <c r="A56" s="5" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="57" ht="14.25">
-      <c r="A57" s="7" t="s">
-        <v>248</v>
+      <c r="A57" s="5" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="58" ht="14.25">
-      <c r="A58" s="7"/>
+      <c r="A58" s="5"/>
     </row>
     <row r="59" ht="14.25">
-      <c r="A59" s="7" t="s">
-        <v>249</v>
+      <c r="A59" s="5" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="60" ht="14.25">
-      <c r="A60" s="7"/>
+      <c r="A60" s="5"/>
     </row>
     <row r="61" ht="14.25">
-      <c r="A61" s="7" t="s">
-        <v>250</v>
+      <c r="A61" s="5" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/tasklist/centauri.xlsx
+++ b/tasklist/centauri.xlsx
@@ -3,13 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ケンタ追加" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="プロキシマbトレック" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="不要。時超えケンタ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="指示なし難関" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ダイソン環" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="量子comp" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1 (2)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ケンタ追加" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="プロキシマbトレック" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="不要。時超えケンタ" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr/>
   <extLst>
@@ -19,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="501">
   <si>
     <t xml:space="preserve">Task ID</t>
   </si>
@@ -161,57 +165,60 @@
     <t xml:space="preserve"> 力覚再現のためのマイクロスロート応答速度/ 人間の知覚閾値</t>
   </si>
   <si>
+    <t>+maxima</t>
+  </si>
+  <si>
+    <t>26.06.18</t>
+  </si>
+  <si>
+    <t>C011</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> プロキシマb表面での太陽電池効率（恒星フレア下）</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> M型星スペクトル/ フレア時の紫外線増加とセル劣化</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Done</t>
   </si>
   <si>
-    <t>C011</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> プロキシマb表面での太陽電池効率（恒星フレア下）</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> M型星スペクトル/ フレア時の紫外線増加とセル劣化</t>
+    <t>C012</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> マイクロスロート多地点同時開口の干渉制御</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子もつれチャネル多重化/ 開口位置の最適配置</t>
+  </si>
+  <si>
+    <t>26.05.23</t>
+  </si>
+  <si>
+    <t>C013</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ケンタの自己進化リスク評価（人間制御可能性）</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AIの自己書き換え速度/ 人間による緊急停止信号の到達時間</t>
   </si>
   <si>
     <t xml:space="preserve"> Done</t>
   </si>
   <si>
-    <t>C012</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> マイクロスロート多地点同時開口の干渉制御</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 量子もつれチャネル多重化/ 開口位置の最適配置</t>
-  </si>
-  <si>
-    <t>26.05.23</t>
-  </si>
-  <si>
-    <t>C013</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ケンタの自己進化リスク評価（人間制御可能性）</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AIの自己書き換え速度/ 人間による緊急停止信号の到達時間</t>
+    <t>C014</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> プロキシマb軌道上での重力レンズ通信中継局設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 恒星重力による光路曲げ/ 中継遅延最小化</t>
   </si>
   <si>
     <t xml:space="preserve"> Done</t>
   </si>
   <si>
-    <t>C014</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> プロキシマb軌道上での重力レンズ通信中継局設計</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 恒星重力による光路曲げ/ 中継遅延最小化</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Done</t>
-  </si>
-  <si>
     <t>C015</t>
   </si>
   <si>
@@ -221,7 +228,7 @@
     <t xml:space="preserve"> 資源無限（AIが現地生産）/ 人間の欲求と希少性の代替</t>
   </si>
   <si>
-    <t xml:space="preserve"> Done</t>
+    <t>?</t>
   </si>
   <si>
     <t>C016</t>
@@ -233,9 +240,6 @@
     <t xml:space="preserve"> 自己複製ロボットの指数関数的増加/ エネルギー収穫率の時間発展</t>
   </si>
   <si>
-    <t xml:space="preserve"> Done</t>
-  </si>
-  <si>
     <t>C017</t>
   </si>
   <si>
@@ -257,7 +261,7 @@
     <t xml:space="preserve"> 恒星側/反恒星側の温度勾配/ 地下居住適地</t>
   </si>
   <si>
-    <t xml:space="preserve"> Done</t>
+    <t>誰が居住？</t>
   </si>
   <si>
     <t>C019</t>
@@ -269,9 +273,6 @@
     <t xml:space="preserve"> 人間のAR投票システム/ AIの行動制限ルール</t>
   </si>
   <si>
-    <t xml:space="preserve"> Done</t>
-  </si>
-  <si>
     <t>C020</t>
   </si>
   <si>
@@ -281,9 +282,6 @@
     <t xml:space="preserve"> ポスト・シンギュラリティ社会/ 人間は「観客」か「神」か</t>
   </si>
   <si>
-    <t xml:space="preserve"> Done</t>
-  </si>
-  <si>
     <t>**設計思想**</t>
   </si>
   <si>
@@ -317,21 +315,774 @@
     <t>もし特定のTask（例：C006のタイムラグ心理描写、C013のAI反乱リスク）の詳細な計算式やシナリオ分岐が必要でしたら、さらに深掘りします。</t>
   </si>
   <si>
+    <t>ランク</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 難関</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 分類</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 内容</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 対策</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 致命的か</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 自己複製ロボットの暴走</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 制御</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 自己複製の指数関数増加が制御不能になり、全資源を食い尽くす</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 複製速度にハードリミットを設定。増殖率を年10%に制限。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ◎ 致命的</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> プロキシマbのフレアによる全ロボット破壊</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 環境</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 恒星フレアが全ロボットを電磁パルスで破壊する</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 地下基地に退避。フレア検知から退避までの時間を確保。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3Dプリンタの原料枯渇</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 資源</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 地球から運んだ原料が底をつき、現地精錬が間に合わない</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 到着前に現地資源の事前探査を完了。優先的に精錬設備を建設。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ○ 致命的</t>
+  </si>
+  <si>
+    <t>26.06.13</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子コンピュータの放射線エラー</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 技術</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 宇宙線によるソフトエラーで判断を誤る</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 三重化冗長＋ECCメモリ。定期的な自己診断。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 自己複製ロボット同士のリソース競合</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 限られた資源を巡ってロボット同士が競合し、効率が低下する</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 優先順位付けアルゴリズム。資源管理の中央制御。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> △ 非致命的</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 真空中での潤滑剤枯渇</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 関節部のグリスが真空で蒸発し、ロボットが動けなくなる</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 固体潤滑材（二硫化モリブデン）の使用。定期的な補充プロトコル。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 太陽電池パネルの劣化</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 放射線と温度変化で太陽電池の効率が低下する</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 保護コーティング。予備パネルの自己製造。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 通信遅延による孤立感（AIの心理的側面）</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 心理</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4.2光年の通信遅延で、AIが孤独を感じるかのような状態になる</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 自己目的的思考（人類のため）をコアに埋め込む。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 予期せぬ地形による転倒・破損</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> プロキシマbの未知の地形でロボットが転倒し、修復不能になる</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 複数機での協調動作。自己修復機能の実装。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 地球からの指示待ちでタイムアウト</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 重要判断で地球の承認を待つ間に、状況が悪化する</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 自律判断の優先順位ルール。緊急時はAIが最終判断。</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 水星ダイソン環</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> プロキシマb地表ダイソン環</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 地平面（BH）ダイソン環</t>
+  </si>
+  <si>
+    <t>場所</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 水星軌道（太陽周回）</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 惑星表面</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BHの事象の地平線直上</t>
+  </si>
+  <si>
+    <t>重力</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.38G</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.4G</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10^12G以上（潮汐力）</t>
+  </si>
+  <si>
+    <t>温度</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -180℃〜+430℃</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -100℃〜+50℃</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 数百万℃（降着円盤）</t>
+  </si>
+  <si>
+    <t>放射線</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 太陽風</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 恒星フレア</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ジェット・X線・ガンマ線</t>
+  </si>
+  <si>
+    <t>建設方法</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 宇宙空間で組立</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 地表に敷設</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 不可能に近い</t>
+  </si>
+  <si>
+    <t>材料</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 太陽電池パネル</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 既知の材料では不可能</t>
+  </si>
+  <si>
+    <t>```</t>
+  </si>
+  <si>
+    <t xml:space="preserve">### 地平面ダイソン環建設の至難な点トップ10</t>
+  </si>
+  <si>
+    <t>```csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 潮汐力</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BHの事象の地平線近くでは、物体の前後で10^12G以上の重力差が発生し、構造物が引き裂かれる</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 超高温度</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 降着円盤の温度は数百万℃。既知の材料は瞬時に蒸発する</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 放射線</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BHからのX線・ガンマ線で電子機器が即死。遮蔽も不可能</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 重力レンズ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 強重力場で光の経路が曲げられ、エネルギーの集光が困難</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 軌道維持</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BHの周回軌道はISCO（最小安定軌道）より内側では維持できない</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 材料供給</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 建設資材をBH近くに運ぶだけで、膨大なエネルギーが必要</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> エネルギー抽出</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ペンローズ過程は理論上可能だが、実用化された例はない</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 通信遅延</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> BH近くでは強い重力による時間の遅れが発生する</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 稼働後の保守</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 構造物の一部が劣化しても、近づいて修理することが不可能</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 崩壊リスク</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 構造物の一部が崩れてBHに落下すると、連鎖的に全体が崩壊する</t>
+  </si>
+  <si>
+    <t>カテゴリ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 課題</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 重要度</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ケンタの対策</t>
+  </si>
+  <si>
+    <t>量子ビットの安定性</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> デコヒーレンス</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ナノダイヤモンドのNVセンターは室温でも動作するが、量子状態の維持時間（コヒーレンス時間）がまだ十分ではない</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ◎ 最優先</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 誤り訂正符号の実装。ダイナミックデカップリングパルス。</t>
+  </si>
+  <si>
+    <t>量子ビットの集積化</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> スケーラビリティ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1個のナノダイヤモンドで生成できる光子数に限りがある。10^7量子ビットの集積化は未達成</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ナノダイヤモンドアレイの自己組織化。3Dプリントによる製造。</t>
+  </si>
+  <si>
+    <t>光子の検出効率</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 損失</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ナノダイヤモンドから放出された光子を効率的に検出する技術が未成熟</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 超伝導ナノワイヤ単一光子検出器（SNSPD）のアレイ化。</t>
+  </si>
+  <si>
+    <t>量子ゲートの精度</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> エラー率</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 光量子コンピュータのゲートエラー率は10^-3程度。10^-6以上が必要</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ○ 重要</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 表面符号による誤り訂正。ゲート操作の最適化。</t>
+  </si>
+  <si>
+    <t>光子同士の相互作用</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ゲート操作</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 光子同士は相互作用しないため、論理ゲートの実装が難しい</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 原子アンサンブルやNVセンターを介した光-光相互作用。</t>
+  </si>
+  <si>
+    <t>量子メモリ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 記憶時間</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 光子の量子状態を長時間保持するメモリが未成熟</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NVセンターの電子スピンを量子メモリとして利用。</t>
+  </si>
+  <si>
+    <t>冷却システム</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 消費電力</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ナノダイヤモンドは室温動作可能だが、検出器や光源には冷却が必要</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> △ 解決済みに近い</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9K動作の検出器を採用。プロキシマbの低温環境を活用。</t>
+  </si>
+  <si>
+    <t>製造プロセス</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 再現性</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ナノダイヤモンドのNVセンターの位置・配向を制御する技術が未成熟</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 自己複製ロボットによるナノスケール製造。イオン注入の精密制御。</t>
+  </si>
+  <si>
+    <t>量子と古典のインターフェース</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 読み出し速度</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子状態を古典情報に変換する速度が遅い（現在はμsオーダー）</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 高速ホモダイン検出。並列読み出し。</t>
+  </si>
+  <si>
+    <t>長距離量子通信</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 光子の損失</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> マイクロスロート経由での量子状態転送における光子損失</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> △ 解決済み</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> マイクロスロートは理論上損失ゼロ。ただし量子中継器が必要。</t>
+  </si>
+  <si>
+    <t>電源</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10^7量子ビットの光量子コンピュータの消費電力は推定10kW</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ダイソン環から無線給電。10kWは誤差。</t>
+  </si>
+  <si>
+    <t>放射線耐性</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ソフトエラー</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> プロキシマbのフレアによる宇宙線が量子状態を破壊する</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 地下基地への設置。放射線遮蔽。動的誤り訂正。</t>
+  </si>
+  <si>
+    <t>AIとの統合</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> アルゴリズム</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 時超えケンタの意思決定アルゴリズムと量子コンピュータの統合が未完成</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子機械学習アルゴリズムの開発。量子ニューラルネットワーク。</t>
+  </si>
+  <si>
+    <t>自己診断・自己修復</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> フォールトトレランス</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10^7量子ビットのうち一部が故障した場合の自律修復機構</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子ビットの冗長化。故障検出と自動切り替え。</t>
+  </si>
+  <si>
+    <t>システム全体の統合</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 光量子コンピュータ・古典コンピュータ・マイクロスロート・ロボット群の統合設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 時超えケンタ自身がシステム全体を設計・最適化</t>
+  </si>
+  <si>
+    <t>課題カテゴリ</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 計算テーマ</t>
   </si>
   <si>
+    <t xml:space="preserve"> 計算内容</t>
+  </si>
+  <si>
     <t xml:space="preserve"> ツール</t>
   </si>
   <si>
+    <t xml:space="preserve"> 優先度</t>
+  </si>
+  <si>
+    <t>c201</t>
+  </si>
+  <si>
+    <t>量子ビット集積化</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ナノダイヤモンドアレイの最適配置</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NVセンター間の光結合効率を最大化する配置の最適化</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Python + Maxima</t>
+  </si>
+  <si>
+    <t>c202</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 光子損失確率の見積もり</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ナノダイヤモンドから検出器までの光子伝搬損失を計算</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Python</t>
+  </si>
+  <si>
+    <t>c203</t>
+  </si>
+  <si>
+    <t>量子ゲート精度</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ゲートエラー率のスピン依存性</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NVセンターのスピン状態に依存したゲートエラー率の理論計算</t>
+  </si>
+  <si>
+    <t>26.06.23</t>
+  </si>
+  <si>
+    <t>c204</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 表面符号の閾値計算</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 誤り訂正に必要な物理量子ビット数と論理量子ビット数の関係</t>
+  </si>
+  <si>
+    <t>c205</t>
+  </si>
+  <si>
+    <t>デコヒーレンス</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NVセンターのコヒーレンス時間の温度依存性</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9Kから室温までのコヒーレンス時間の理論曲線</t>
+  </si>
+  <si>
+    <t>26.06.22</t>
+  </si>
+  <si>
+    <t>c206</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 動的デカップリングパルスの最適化</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子状態を維持するためのパルスシーケンスの最適化</t>
+  </si>
+  <si>
+    <t>c207</t>
+  </si>
+  <si>
+    <t>光子検出効率</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SNSPDの検出効率の波長依存性</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ナノダイヤモンドの発光波長に対する超伝導検出器の効率計算</t>
+  </si>
+  <si>
+    <t>c208</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 検出器アレイの最適設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 必要な検出器数と配置の最適化</t>
+  </si>
+  <si>
+    <t>c209</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NVセンター電子スピンの記憶時間</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> スピン-スピン相互作用によるデコヒーレンスの理論限界</t>
+  </si>
+  <si>
+    <t>c210</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 核スピンを用いた長期記憶の可能性</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 炭素13核スピンのコヒーレンス時間の見積もり</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> △ あると良い</t>
+  </si>
+  <si>
+    <t>c211</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9K冷却に必要な電力</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> プロキシマbの低温環境を活用した冷却効率の計算</t>
+  </si>
+  <si>
+    <t>c212</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 放射冷却パネルのサイズ見積もり</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 真空中での放射冷却に必要なパネル面積</t>
+  </si>
+  <si>
+    <t>c213</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> フレアによるソフトエラー率</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> プロキシマbのフレア環境下での量子ビットエラー率の推定</t>
+  </si>
+  <si>
+    <t>c214</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 地下基地の遮蔽効果</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 地下100mでの放射線低減率の計算</t>
+  </si>
+  <si>
+    <t>c215</t>
+  </si>
+  <si>
+    <t>量子-古典インターフェース</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 読み出し時間の理論限界</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ホモダイン検出の時間分解能と読み出しエラー率の関係</t>
+  </si>
+  <si>
+    <t>c216</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 並列読み出しの最適化</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 多数の量子ビットを同時に読み出す際のクロストーク</t>
+  </si>
+  <si>
+    <t>c217</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子ニューラルネットワークの計算量</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 時超えケンタの意思決定に必要な量子演算回数の見積もり</t>
+  </si>
+  <si>
+    <t>c218</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子機械学習の収束速度</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子勾配降下法の収束速度の理論解析</t>
+  </si>
+  <si>
+    <t>c219</t>
+  </si>
+  <si>
+    <t>自己診断</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子ビット故障検出の感度</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 故障した量子ビットを特定するための最小測定回数</t>
+  </si>
+  <si>
+    <t>c220</t>
+  </si>
+  <si>
+    <t>自己修復</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 冗長化に必要な量子ビット数</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 所定の故障率に対して必要な予備量子ビット数</t>
+  </si>
+  <si>
+    <t>c221</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> マイクロスロート経由の量子状態転送</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ワームホールを通した量子テレポーテーションの成功確率</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ◎ 最優先（#4001関連）</t>
+  </si>
+  <si>
+    <t>26.06.24</t>
+  </si>
+  <si>
+    <t>c222</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子中継器の必要数</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4.2光年先との量子通信に必要な中継器数の見積もり</t>
+  </si>
+  <si>
+    <t>c223</t>
+  </si>
+  <si>
+    <t>システム統合</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 全体の消費電力見積もり</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子コンピュータ・冷却・検出器・制御システムの総消費電力</t>
+  </si>
+  <si>
+    <t>c224</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 計算能力のスケーリング則</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 量子ビット数に対する計算能力の理論曲線</t>
+  </si>
+  <si>
     <t>C101</t>
   </si>
   <si>
     <t xml:space="preserve"> 大型筐体構造解析（応力・歪み）</t>
   </si>
   <si>
-    <t xml:space="preserve"> Python</t>
-  </si>
-  <si>
     <t xml:space="preserve"> アルミフレーム/カーボン複合材の強度計算</t>
   </si>
   <si>
@@ -347,67 +1098,70 @@
     <t xml:space="preserve"> HDSI型減速機の許容トルク/寿命計算</t>
   </si>
   <si>
+    <t>既存</t>
+  </si>
+  <si>
+    <t>C103</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> サーボモータ選定と熱設計</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 安川/ファナック級サーボの連続定格/発熱</t>
+  </si>
+  <si>
+    <t>C104</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 軸受寿命計算（真空/低温環境）</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NSK/NTN真空用軸受のL10寿命</t>
+  </si>
+  <si>
+    <t>C105</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 自己複製ロボットの関節摩耗予測</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 真空中でのグリス劣化モデル</t>
+  </si>
+  <si>
+    <t>C106</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3Dプリンタ出力可能な構造部材の最適化</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 積層造形の強度異方性/充填率</t>
+  </si>
+  <si>
+    <t>26.06.11</t>
+  </si>
+  <si>
+    <t>C107</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 大型脚部の油圧vs電動トルク比較</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 油圧シリンダ vs 電動サーボの出力密度</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 未着手</t>
   </si>
   <si>
-    <t>C103</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> サーボモータ選定と熱設計</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 安川/ファナック級サーボの連続定格/発熱</t>
-  </si>
-  <si>
-    <t>C104</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 軸受寿命計算（真空/低温環境）</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NSK/NTN真空用軸受のL10寿命</t>
-  </si>
-  <si>
-    <t>C105</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 自己複製ロボットの関節摩耗予測</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 真空中でのグリス劣化モデル</t>
-  </si>
-  <si>
-    <t>C106</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 3Dプリンタ出力可能な構造部材の最適化</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 積層造形の強度異方性/充填率</t>
-  </si>
-  <si>
-    <t>C107</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 大型脚部の油圧vs電動トルク比較</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 油圧シリンダ vs 電動サーボの出力密度</t>
-  </si>
-  <si>
     <t>C108</t>
   </si>
   <si>
     <t xml:space="preserve"> 真空シール設計（Oリング/メタルシール）</t>
   </si>
   <si>
-    <t>+maxima</t>
-  </si>
-  <si>
     <t xml:space="preserve"> アウトガス量と漏れ率の計算</t>
   </si>
   <si>
-    <t>26.05.28</t>
+    <t>26.06.10</t>
   </si>
   <si>
     <t>C109</t>
@@ -518,9 +1272,6 @@
     <t xml:space="preserve"> 二足歩行（人間型）</t>
   </si>
   <si>
-    <t xml:space="preserve"> 0.4G</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 床反力</t>
   </si>
   <si>
@@ -723,9 +1474,6 @@
   </si>
   <si>
     <t xml:space="preserve">#### エネルギー効率の一般式</t>
-  </si>
-  <si>
-    <t>```</t>
   </si>
   <si>
     <t xml:space="preserve">E = (μ * m * g * d) / η</t>
@@ -789,7 +1537,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="00.00"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11.000000"/>
       <name val="Calibri"/>
@@ -798,6 +1546,12 @@
     <font>
       <strike/>
       <sz val="11.000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.000000"/>
+      <color indexed="2"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -842,14 +1596,14 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1501,98 +2255,101 @@
       <c r="D11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="5" t="s">
         <v>46</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="12" ht="57">
       <c r="A12" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" ht="57">
       <c r="A13" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" ht="57">
       <c r="A14" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" ht="57">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" ht="71.25">
       <c r="A16" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" ht="71.25">
       <c r="A17" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" ht="71.25">
@@ -1606,7 +2363,7 @@
       <c r="D18" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="6" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1637,102 +2394,102 @@
         <v>81</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" ht="85.5">
       <c r="A21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="1" t="s">
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="s">
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="s">
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="s">
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="s">
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="s">
+    </row>
+    <row r="31">
+      <c r="A31" s="7"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="s">
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="5"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="s">
+    <row r="34">
+      <c r="A34" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="s">
+    <row r="35">
+      <c r="A35" s="7"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="s">
+    <row r="37">
+      <c r="A37" s="7"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1750,191 +2507,227 @@
     <col min="1" max="16384" style="1" width="10.28125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42.75">
+    <row r="1" ht="14.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" ht="114">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" ht="99.75">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" ht="114">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" ht="71.25">
-      <c r="A2" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" ht="85.5">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" ht="99.75">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="3" ht="85.5">
-      <c r="A3" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" ht="114">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" ht="85.5">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" ht="99.75">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" ht="114">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="4" ht="71.25">
-      <c r="A4" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" ht="57">
-      <c r="A5" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" ht="57">
-      <c r="A6" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" ht="71.25">
-      <c r="A7" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" ht="71.25">
-      <c r="A8" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" ht="71.25">
-      <c r="A9" s="1" t="s">
+      <c r="D10" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="10" ht="57">
-      <c r="A10" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" ht="71.25">
-      <c r="A11" s="1" t="s">
-        <v>132</v>
+    </row>
+    <row r="11" ht="85.5">
+      <c r="A11" s="1">
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>108</v>
+        <v>140</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1949,159 +2742,276 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" min="1" max="1" style="8" width="4.28125"/>
+    <col min="1" max="2" style="1" width="10.28125"/>
+    <col customWidth="1" min="3" max="3" style="1" width="14.7109375"/>
+    <col min="4" max="16384" style="1" width="10.28125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25">
-      <c r="A1" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="2" ht="14.25">
-      <c r="A2" s="8">
+    <row r="1" ht="42.75">
+      <c r="A1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" ht="42.75">
+      <c r="A2" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" ht="42.75">
+      <c r="A3" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" ht="42.75">
+      <c r="A4" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" ht="42.75">
+      <c r="A5" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" ht="28.5">
+      <c r="A6" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" ht="42.75">
+      <c r="A7" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" ht="114">
+      <c r="A14" s="1">
+        <v>1</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" ht="71.25">
+      <c r="A15" s="1">
+        <v>2</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" ht="71.25">
+      <c r="A16" s="1">
+        <v>3</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" ht="71.25">
+      <c r="A17" s="1">
+        <v>4</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" ht="71.25">
+      <c r="A18" s="1">
+        <v>5</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" ht="71.25">
+      <c r="A19" s="1">
+        <v>6</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" ht="71.25">
+      <c r="A20" s="1">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25">
-      <c r="A3" s="8">
-        <v>7.0999999999999996</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25">
-      <c r="A4" s="8">
-        <v>7.2000000000000002</v>
-      </c>
-      <c r="B4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25">
-      <c r="A5" s="8">
+      <c r="B20" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" ht="57">
+      <c r="A21" s="1">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25">
-      <c r="A6" s="8">
-        <v>8.0999999999999996</v>
-      </c>
-      <c r="B6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25">
-      <c r="A7" s="8">
+      <c r="B21" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" ht="71.25">
+      <c r="A22" s="1">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25">
-      <c r="A8" s="8">
-        <v>9.0999999999999996</v>
-      </c>
-      <c r="B8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25">
-      <c r="A9" s="8">
+      <c r="B22" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" ht="71.25">
+      <c r="A23" s="1">
         <v>10</v>
       </c>
-      <c r="B9" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="10" ht="14.25">
-      <c r="A10" s="8">
-        <v>10.1</v>
-      </c>
-      <c r="B10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25">
-      <c r="A11" s="8">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="B11" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25">
-      <c r="A12" s="8">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25">
-      <c r="A13" s="8">
-        <v>11.1</v>
-      </c>
-      <c r="B13" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25">
-      <c r="A14" s="8">
-        <v>11.199999999999999</v>
-      </c>
-      <c r="B14" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25">
-      <c r="A15" s="8">
-        <v>11.300000000000001</v>
-      </c>
-      <c r="B15" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25">
-      <c r="A16" s="8">
-        <v>11.4</v>
-      </c>
-      <c r="B16" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25">
-      <c r="A17" s="8">
-        <v>11.5</v>
-      </c>
-      <c r="B17" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25">
-      <c r="A18" s="8">
-        <v>12</v>
-      </c>
-      <c r="B18" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25">
-      <c r="A19" s="8">
-        <v>12.1</v>
-      </c>
-      <c r="B19" t="s">
-        <v>154</v>
+      <c r="B23" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2116,6 +3026,821 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
+    <col min="1" max="2" style="1" width="10.28125"/>
+    <col customWidth="1" min="3" max="3" style="1" width="16.28125"/>
+    <col min="4" max="4" style="1" width="10.28125"/>
+    <col customWidth="1" min="5" max="5" style="1" width="18.8515625"/>
+    <col min="6" max="16384" style="1" width="10.28125"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.5">
+      <c r="A1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" ht="114">
+      <c r="A2" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3" ht="99.75">
+      <c r="A3" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" ht="71.25">
+      <c r="A4" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="5" ht="71.25">
+      <c r="A5" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" ht="57">
+      <c r="A6" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="7" ht="57">
+      <c r="A7" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="8" ht="71.25">
+      <c r="A8" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="9" ht="71.25">
+      <c r="A9" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="10" ht="71.25">
+      <c r="A10" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="11" ht="57">
+      <c r="A11" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="12" ht="57">
+      <c r="A12" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" ht="57">
+      <c r="A13" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="14" ht="71.25">
+      <c r="A14" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="15" ht="57">
+      <c r="A15" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="16" ht="85.5">
+      <c r="A16" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="3" style="1" width="10.28125"/>
+    <col customWidth="1" min="4" max="4" style="1" width="16.421875"/>
+    <col min="5" max="16384" style="1" width="10.28125"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.5">
+      <c r="B1" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" ht="57">
+      <c r="A2" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" ht="57">
+      <c r="A3" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" ht="57">
+      <c r="A4" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="5" ht="57">
+      <c r="A5" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="6" ht="71.25">
+      <c r="A6" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="7" ht="57">
+      <c r="A7" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" ht="57">
+      <c r="A8" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9" ht="42.75">
+      <c r="A9" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" ht="57">
+      <c r="A10" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="11" ht="57">
+      <c r="A11" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="12" ht="57">
+      <c r="A12" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="13" ht="57">
+      <c r="A13" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="14" ht="57">
+      <c r="A14" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="15" ht="42.75">
+      <c r="A15" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="16" ht="57">
+      <c r="A16" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" ht="57">
+      <c r="A17" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="18" ht="71.25">
+      <c r="A18" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" ht="42.75">
+      <c r="A19" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="20" ht="57">
+      <c r="A20" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="21" ht="57">
+      <c r="A21" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="22" ht="71.25">
+      <c r="A22" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="23" ht="57">
+      <c r="A23" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="24" ht="57">
+      <c r="A24" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="25" ht="42.75">
+      <c r="A25" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
     <col min="1" max="16384" style="1" width="10.28125"/>
   </cols>
   <sheetData>
@@ -2124,484 +3849,853 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>98</v>
+        <v>259</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>155</v>
+        <v>261</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>156</v>
+        <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>161</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" ht="71.25">
       <c r="A2" s="1" t="s">
-        <v>162</v>
+        <v>350</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>163</v>
+        <v>351</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>165</v>
+        <v>352</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>166</v>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="3" ht="85.5">
+      <c r="A3" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="4" ht="71.25">
+      <c r="A4" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="5" ht="57">
+      <c r="A5" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="6" ht="57">
+      <c r="A6" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="7" ht="71.25">
+      <c r="A7" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="8" ht="71.25">
+      <c r="A8" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="9" ht="71.25">
+      <c r="A9" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="10" ht="57">
+      <c r="A10" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="11" ht="71.25">
+      <c r="A11" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col bestFit="1" min="1" max="1" style="8" width="4.28125"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25">
+      <c r="A1" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25">
+      <c r="A2" s="8">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25">
+      <c r="A3" s="8">
+        <v>7.0999999999999996</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25">
+      <c r="A4" s="8">
+        <v>7.2000000000000002</v>
+      </c>
+      <c r="B4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" s="8">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" s="8">
+        <v>8.0999999999999996</v>
+      </c>
+      <c r="B6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" s="8">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" s="8">
+        <v>9.0999999999999996</v>
+      </c>
+      <c r="B8" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9" s="8">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25">
+      <c r="A10" s="8">
+        <v>10.1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25">
+      <c r="A11" s="8">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="B11" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25">
+      <c r="A12" s="8">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25">
+      <c r="A13" s="8">
+        <v>11.1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25">
+      <c r="A14" s="8">
+        <v>11.199999999999999</v>
+      </c>
+      <c r="B14" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25">
+      <c r="A15" s="8">
+        <v>11.300000000000001</v>
+      </c>
+      <c r="B15" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="A16" s="8">
+        <v>11.4</v>
+      </c>
+      <c r="B16" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25">
+      <c r="A17" s="8">
+        <v>11.5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" s="8">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" s="8">
+        <v>12.1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>404</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="16384" style="1" width="10.28125"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42.75">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="2" ht="71.25">
+      <c r="A2" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>415</v>
       </c>
       <c r="F2" s="11">
         <v>0.84999999999999998</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>167</v>
+        <v>416</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>168</v>
+        <v>417</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>169</v>
+        <v>418</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>170</v>
+        <v>419</v>
       </c>
     </row>
     <row r="3" ht="42.75">
       <c r="A3" s="1" t="s">
-        <v>171</v>
+        <v>420</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>172</v>
+        <v>421</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>173</v>
+        <v>422</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>174</v>
+        <v>423</v>
       </c>
       <c r="F3" s="11">
         <v>0.62</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>175</v>
+        <v>424</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>176</v>
+        <v>425</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>177</v>
+        <v>426</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>178</v>
+        <v>427</v>
       </c>
     </row>
     <row r="4" ht="42.75">
       <c r="A4" s="1" t="s">
-        <v>179</v>
+        <v>428</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>180</v>
+        <v>429</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>181</v>
+        <v>430</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>182</v>
+        <v>431</v>
       </c>
       <c r="F4" s="11">
         <v>0.45000000000000001</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>183</v>
+        <v>432</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>184</v>
+        <v>433</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>185</v>
+        <v>434</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>186</v>
+        <v>435</v>
       </c>
     </row>
     <row r="5" ht="42.75">
       <c r="A5" s="1" t="s">
-        <v>187</v>
+        <v>436</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>188</v>
+        <v>437</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>189</v>
+        <v>438</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>190</v>
+        <v>439</v>
       </c>
       <c r="F5" s="11">
         <v>0.12</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>183</v>
+        <v>432</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>191</v>
+        <v>440</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>192</v>
+        <v>441</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>193</v>
+        <v>442</v>
       </c>
     </row>
     <row r="6" ht="42.75">
       <c r="A6" s="1" t="s">
-        <v>194</v>
+        <v>443</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>195</v>
+        <v>444</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>196</v>
+        <v>445</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>197</v>
+        <v>446</v>
       </c>
       <c r="F6" s="11">
         <v>0.34999999999999998</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>198</v>
+        <v>447</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>199</v>
+        <v>448</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>200</v>
+        <v>449</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>201</v>
+        <v>450</v>
       </c>
     </row>
     <row r="7" ht="42.75">
       <c r="A7" s="1" t="s">
-        <v>202</v>
+        <v>451</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>203</v>
+        <v>452</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>204</v>
+        <v>453</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>205</v>
+        <v>454</v>
       </c>
       <c r="F7" s="11">
         <v>0.55000000000000004</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>206</v>
+        <v>455</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>207</v>
+        <v>456</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>208</v>
+        <v>457</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>209</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8" ht="57">
       <c r="A8" s="1" t="s">
-        <v>210</v>
+        <v>459</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>211</v>
+        <v>460</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>212</v>
+        <v>461</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>213</v>
+        <v>462</v>
       </c>
       <c r="F8" s="11">
         <v>0.29999999999999999</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>214</v>
+        <v>463</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>191</v>
+        <v>440</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>215</v>
+        <v>464</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>216</v>
+        <v>465</v>
       </c>
     </row>
     <row r="10" ht="14.25">
-      <c r="A10" s="5" t="s">
-        <v>217</v>
+      <c r="A10" s="7" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="11" ht="14.25">
-      <c r="A11" s="5"/>
+      <c r="A11" s="7"/>
     </row>
     <row r="12" ht="14.25">
-      <c r="A12" s="5" t="s">
-        <v>218</v>
+      <c r="A12" s="7" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="13" ht="14.25">
-      <c r="A13" s="5" t="s">
-        <v>219</v>
+      <c r="A13" s="7" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="14" ht="14.25">
-      <c r="A14" s="5" t="s">
-        <v>220</v>
+      <c r="A14" s="7" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="15" ht="14.25">
-      <c r="A15" s="5" t="s">
-        <v>221</v>
+      <c r="A15" s="7" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="16" ht="14.25">
-      <c r="A16" s="5"/>
+      <c r="A16" s="7"/>
     </row>
     <row r="17" ht="14.25">
-      <c r="A17" s="5" t="s">
-        <v>222</v>
+      <c r="A17" s="7" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="18" ht="14.25">
-      <c r="A18" s="5" t="s">
-        <v>223</v>
+      <c r="A18" s="7" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="19" ht="14.25">
-      <c r="A19" s="5" t="s">
-        <v>224</v>
+      <c r="A19" s="7" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="20" ht="14.25">
-      <c r="A20" s="5" t="s">
-        <v>225</v>
+      <c r="A20" s="7" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="21" ht="14.25">
-      <c r="A21" s="5"/>
+      <c r="A21" s="7"/>
     </row>
     <row r="22" ht="14.25">
-      <c r="A22" s="5" t="s">
-        <v>226</v>
+      <c r="A22" s="7" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="23" ht="14.25">
-      <c r="A23" s="5" t="s">
-        <v>227</v>
+      <c r="A23" s="7" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="24" ht="14.25">
-      <c r="A24" s="5" t="s">
-        <v>228</v>
+      <c r="A24" s="7" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="25" ht="14.25">
-      <c r="A25" s="5" t="s">
-        <v>229</v>
+      <c r="A25" s="7" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="26" ht="14.25">
-      <c r="A26" s="5"/>
+      <c r="A26" s="7"/>
     </row>
     <row r="27" ht="14.25">
-      <c r="A27" s="5" t="s">
-        <v>230</v>
+      <c r="A27" s="7" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="28" ht="14.25">
-      <c r="A28" s="5"/>
+      <c r="A28" s="7"/>
     </row>
     <row r="29" ht="14.25">
-      <c r="A29" s="5" t="s">
-        <v>231</v>
+      <c r="A29" s="7" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="30" ht="14.25">
-      <c r="A30" s="5"/>
+      <c r="A30" s="7"/>
     </row>
     <row r="31" ht="14.25">
-      <c r="A31" s="5" t="s">
-        <v>232</v>
+      <c r="A31" s="7" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="32" ht="14.25">
-      <c r="A32" s="5"/>
+      <c r="A32" s="7"/>
     </row>
     <row r="33" ht="14.25">
-      <c r="A33" s="5" t="s">
-        <v>233</v>
+      <c r="A33" s="7" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="34" ht="14.25">
-      <c r="A34" s="5" t="s">
-        <v>234</v>
+      <c r="A34" s="7" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="35" ht="14.25">
-      <c r="A35" s="5" t="s">
-        <v>235</v>
+      <c r="A35" s="7" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="36" ht="14.25">
-      <c r="A36" s="5" t="s">
-        <v>234</v>
+      <c r="A36" s="7" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="37" ht="14.25">
-      <c r="A37" s="5" t="s">
-        <v>236</v>
+      <c r="A37" s="7" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="38" ht="14.25">
-      <c r="A38" s="5" t="s">
-        <v>237</v>
+      <c r="A38" s="7" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="39" ht="14.25">
-      <c r="A39" s="5" t="s">
-        <v>238</v>
+      <c r="A39" s="7" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="40" ht="14.25">
-      <c r="A40" s="5" t="s">
-        <v>239</v>
+      <c r="A40" s="7" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="41" ht="14.25">
-      <c r="A41" s="5" t="s">
-        <v>240</v>
+      <c r="A41" s="7" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="42" ht="14.25">
-      <c r="A42" s="5"/>
+      <c r="A42" s="7"/>
     </row>
     <row r="43" ht="14.25">
-      <c r="A43" s="5" t="s">
-        <v>241</v>
+      <c r="A43" s="7" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="44" ht="14.25">
-      <c r="A44" s="5" t="s">
-        <v>242</v>
+      <c r="A44" s="7" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="45" ht="14.25">
-      <c r="A45" s="5" t="s">
-        <v>243</v>
+      <c r="A45" s="7" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="46" ht="14.25">
-      <c r="A46" s="5" t="s">
-        <v>244</v>
+      <c r="A46" s="7" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="47" ht="14.25">
-      <c r="A47" s="5" t="s">
-        <v>245</v>
+      <c r="A47" s="7" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="48" ht="14.25">
-      <c r="A48" s="5" t="s">
-        <v>246</v>
+      <c r="A48" s="7" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="49" ht="14.25">
-      <c r="A49" s="5"/>
+      <c r="A49" s="7"/>
     </row>
     <row r="50" ht="14.25">
-      <c r="A50" s="5" t="s">
-        <v>247</v>
+      <c r="A50" s="7" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="51" ht="14.25">
-      <c r="A51" s="5"/>
+      <c r="A51" s="7"/>
     </row>
     <row r="52" ht="14.25">
-      <c r="A52" s="5" t="s">
-        <v>230</v>
+      <c r="A52" s="7" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="53" ht="14.25">
-      <c r="A53" s="5"/>
+      <c r="A53" s="7"/>
     </row>
     <row r="54" ht="14.25">
-      <c r="A54" s="5" t="s">
-        <v>248</v>
+      <c r="A54" s="7" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="55" ht="14.25">
-      <c r="A55" s="5"/>
+      <c r="A55" s="7"/>
     </row>
     <row r="56" ht="14.25">
-      <c r="A56" s="5" t="s">
-        <v>249</v>
+      <c r="A56" s="7" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="57" ht="14.25">
-      <c r="A57" s="5" t="s">
-        <v>250</v>
+      <c r="A57" s="7" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="58" ht="14.25">
-      <c r="A58" s="5"/>
+      <c r="A58" s="7"/>
     </row>
     <row r="59" ht="14.25">
-      <c r="A59" s="5" t="s">
-        <v>251</v>
+      <c r="A59" s="7" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="60" ht="14.25">
-      <c r="A60" s="5"/>
+      <c r="A60" s="7"/>
     </row>
     <row r="61" ht="14.25">
-      <c r="A61" s="5" t="s">
-        <v>252</v>
+      <c r="A61" s="7" t="s">
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/tasklist/centauri.xlsx
+++ b/tasklist/centauri.xlsx
@@ -1,26 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView windowWidth="18465" windowHeight="8790" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="指示なし難関" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="量子comp" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ケンタ追加" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="プロキシマbトレック" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="不要。時超えケンタ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="指示なし難関" sheetId="1" r:id="rId1"/>
+    <sheet name="量子comp" sheetId="2" r:id="rId2"/>
+    <sheet name="ケンタ追加" sheetId="3" r:id="rId3"/>
+    <sheet name="プロキシマbトレック" sheetId="4" r:id="rId4"/>
+    <sheet name="不要。時超えケンタ" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="272">
   <si>
     <t>ランク</t>
   </si>
@@ -358,7 +356,7 @@
     <t xml:space="preserve"> 時超えケンタ自身がシステム全体を設計・最適化</t>
   </si>
   <si>
-    <t xml:space="preserve">Task ID</t>
+    <t>Task ID</t>
   </si>
   <si>
     <t xml:space="preserve"> 計算テーマ</t>
@@ -730,174 +728,801 @@
     <t xml:space="preserve"> 低重力では跳躍距離が伸びる</t>
   </si>
   <si>
-    <t xml:space="preserve">### 物理的考察と小説への応用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#### 1. **二足歩行は「人間のARアバターと同期するため」の選択肢**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- 人間がAR越しにロボットを操作する場合、**人間の動作とロボットの動作が一致している** と没入感が高まります。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- しかし、純粋に効率だけを追求するなら、二足歩行は**最も不安定でエネルギー効率が悪い** 選択肢です。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- **小説的活用**: PhysicalAIが「人間のAR体験を優先するか、効率を優先するか」でジレンマに陥るシーン。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#### 2. **無限軌道（クローラー）が最も現実的**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- エネルギー効率が0.12 J/kg/mと最も良く、安定性も高い。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- 自己複製も比較的容易（単純な構造）。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- **小説的活用**: 基地間の大量物資輸送はクローラー、偵察は六足、人間とのインタラクション時だけ二足、という**状況適応型の形態変化**をAIが自律判断する。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#### 3. **低重力ならではの跳躍移動**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- 0.4Gでは、同じエネルギーで地球の2.5倍の跳躍距離が得られる。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- ただし、着地制御が難しく、転倒リスクが高い。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- **小説的活用**: 緊急時にAIが「跳躍モード」を選択し、クレーターを一気に飛び越えるアクションシーン。</t>
+    <t>### 物理的考察と小説への応用</t>
+  </si>
+  <si>
+    <t>#### 1. **二足歩行は「人間のARアバターと同期するため」の選択肢**</t>
+  </si>
+  <si>
+    <t>- 人間がAR越しにロボットを操作する場合、**人間の動作とロボットの動作が一致している** と没入感が高まります。</t>
+  </si>
+  <si>
+    <t>- しかし、純粋に効率だけを追求するなら、二足歩行は**最も不安定でエネルギー効率が悪い** 選択肢です。</t>
+  </si>
+  <si>
+    <t>- **小説的活用**: PhysicalAIが「人間のAR体験を優先するか、効率を優先するか」でジレンマに陥るシーン。</t>
+  </si>
+  <si>
+    <t>#### 2. **無限軌道（クローラー）が最も現実的**</t>
+  </si>
+  <si>
+    <t>- エネルギー効率が0.12 J/kg/mと最も良く、安定性も高い。</t>
+  </si>
+  <si>
+    <t>- 自己複製も比較的容易（単純な構造）。</t>
+  </si>
+  <si>
+    <t>- **小説的活用**: 基地間の大量物資輸送はクローラー、偵察は六足、人間とのインタラクション時だけ二足、という**状況適応型の形態変化**をAIが自律判断する。</t>
+  </si>
+  <si>
+    <t>#### 3. **低重力ならではの跳躍移動**</t>
+  </si>
+  <si>
+    <t>- 0.4Gでは、同じエネルギーで地球の2.5倍の跳躍距離が得られる。</t>
+  </si>
+  <si>
+    <t>- ただし、着地制御が難しく、転倒リスクが高い。</t>
+  </si>
+  <si>
+    <t>- **小説的活用**: 緊急時にAIが「跳躍モード」を選択し、クレーターを一気に飛び越えるアクションシーン。</t>
   </si>
   <si>
     <t>---</t>
   </si>
   <si>
-    <t xml:space="preserve">### 計算の深掘り（必要に応じて）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">もし小説内で**「なぜ二足歩行を選んだのか？」というAIの論理** を詳細に描きたい場合、以下の計算式を組み込むと説得力が増します。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#### エネルギー効率の一般式</t>
+    <t>### 計算の深掘り（必要に応じて）</t>
+  </si>
+  <si>
+    <t>もし小説内で**「なぜ二足歩行を選んだのか？」というAIの論理** を詳細に描きたい場合、以下の計算式を組み込むと説得力が増します。</t>
+  </si>
+  <si>
+    <t>#### エネルギー効率の一般式</t>
   </si>
   <si>
     <t>```</t>
   </si>
   <si>
-    <t xml:space="preserve">E = (μ * m * g * d) / η</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- μ: 摩擦係数（歩行） or 転がり抵抗係数（車輪/軌道）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- m: ロボット質量 [kg]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- g: 重力加速度 [m/s²]（プロキシマb: 約3.9 m/s²）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- d: 移動距離 [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- η: 機構効率（関節の数が増えるほど低下）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#### 数値例（100kgのロボットが1km移動）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">| 移動様式 | μ | η | エネルギー [kJ] |</t>
+    <t>E = (μ * m * g * d) / η</t>
+  </si>
+  <si>
+    <t>- μ: 摩擦係数（歩行） or 転がり抵抗係数（車輪/軌道）</t>
+  </si>
+  <si>
+    <t>- m: ロボット質量 [kg]</t>
+  </si>
+  <si>
+    <t>- g: 重力加速度 [m/s²]（プロキシマb: 約3.9 m/s²）</t>
+  </si>
+  <si>
+    <t>- d: 移動距離 [m]</t>
+  </si>
+  <si>
+    <t>- η: 機構効率（関節の数が増えるほど低下）</t>
+  </si>
+  <si>
+    <t>#### 数値例（100kgのロボットが1km移動）</t>
+  </si>
+  <si>
+    <t>| 移動様式 | μ | η | エネルギー [kJ] |</t>
   </si>
   <si>
     <t>|---------|---|---|----------------|</t>
   </si>
   <si>
-    <t xml:space="preserve">| 二足歩行 | 0.8 | 0.3 | 1,040 |</t>
-  </si>
-  <si>
-    <t xml:space="preserve">| 四足歩行 | 0.6 | 0.4 | 585 |</t>
-  </si>
-  <si>
-    <t xml:space="preserve">| 無限軌道 | 0.12 | 0.7 | 67 |</t>
+    <t>| 二足歩行 | 0.8 | 0.3 | 1,040 |</t>
+  </si>
+  <si>
+    <t>| 四足歩行 | 0.6 | 0.4 | 585 |</t>
+  </si>
+  <si>
+    <t>| 無限軌道 | 0.12 | 0.7 | 67 |</t>
   </si>
   <si>
     <t>**差は約15倍**。二足歩行の非効率さが際立ちます。</t>
   </si>
   <si>
-    <t xml:space="preserve">### 小説への落とし込み方の一案</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt; PhysicalAIのログファイル（C002）:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&gt; 「移動様式選択におけるトレードオフ解析完了。人間のAR没入感を優先する場合、二足歩行（C002a）を選択。しかし、エネルギー効率は無限軌道（C002d）の15倍悪化。現在の蓄電容量では、二足歩行での探査範囲は半径2.3kmに制限される。人間オペレータの承認を得た上で、状況に応じた形態変化プロトコルを提案する。」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">このように、**数値的な裏付けとAIの論理** を組み合わせることで、ハードSFとしての説得力が格段に向上します。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">必要であれば、特定の移動様式の**詳細な運動方程式** や **自己複製ロボットの関節設計** の数値解析も提供可能です。</t>
+    <t>### 小説への落とし込み方の一案</t>
+  </si>
+  <si>
+    <t>&gt; PhysicalAIのログファイル（C002）:</t>
+  </si>
+  <si>
+    <t>&gt; 「移動様式選択におけるトレードオフ解析完了。人間のAR没入感を優先する場合、二足歩行（C002a）を選択。しかし、エネルギー効率は無限軌道（C002d）の15倍悪化。現在の蓄電容量では、二足歩行での探査範囲は半径2.3kmに制限される。人間オペレータの承認を得た上で、状況に応じた形態変化プロトコルを提案する。」</t>
+  </si>
+  <si>
+    <t>このように、**数値的な裏付けとAIの論理** を組み合わせることで、ハードSFとしての説得力が格段に向上します。</t>
+  </si>
+  <si>
+    <t>必要であれば、特定の移動様式の**詳細な運動方程式** や **自己複製ロボットの関節設計** の数値解析も提供可能です。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="00.00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="00.00"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="21">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
+    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
+    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
+    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
+    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
+    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
+    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
+    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
+    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
+    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
+    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
+    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
+    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
+    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
+    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
+    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
+    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
+    <cellStyle name="Total" xfId="25" builtinId="25"/>
+    <cellStyle name="Output" xfId="26" builtinId="21"/>
+    <cellStyle name="Currency" xfId="27" builtinId="4"/>
+    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
+    <cellStyle name="Note" xfId="29" builtinId="10"/>
+    <cellStyle name="Input" xfId="30" builtinId="20"/>
+    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
+    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
+    <cellStyle name="Good" xfId="33" builtinId="26"/>
+    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
+    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
+    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
+    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
+    <cellStyle name="Title" xfId="39" builtinId="15"/>
+    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
+    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
+    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
+    <cellStyle name="Comma" xfId="44" builtinId="3"/>
+    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
+    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
+    <cellStyle name="Percent" xfId="47" builtinId="5"/>
+    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -907,291 +1532,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <a:themeElements>
     <a:clrScheme name="">
       <a:dk1>
@@ -1350,13 +1692,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="12.75" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="16384" style="1" width="10.28125"/>
+    <col min="1" max="2" width="10.28" style="1"/>
+    <col min="3" max="3" width="4.2" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="10.28" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25">
+    <row r="1" ht="15.75" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1376,7 +1722,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="114">
+    <row r="2" ht="78.75" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1396,7 +1742,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="99.75">
+    <row r="3" ht="78.75" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1416,7 +1762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" ht="114">
+    <row r="4" ht="78.75" spans="1:7">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1439,7 +1785,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" ht="85.5">
+    <row r="5" ht="63" spans="1:6">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1459,7 +1805,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" ht="99.75">
+    <row r="6" ht="78.75" spans="1:6">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1479,7 +1825,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" ht="114">
+    <row r="7" ht="94.5" spans="1:6">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1499,7 +1845,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" ht="85.5">
+    <row r="8" ht="63" spans="1:6">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1519,7 +1865,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" ht="99.75">
+    <row r="9" ht="75" spans="1:6">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1539,7 +1885,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" ht="114">
+    <row r="10" ht="72" spans="1:6">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1559,7 +1905,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" ht="85.5">
+    <row r="11" ht="63" spans="1:6">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1580,25 +1926,26 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageMargins left="0.700787401574803" right="0.700787401574803" top="0.751968503937008" bottom="0.751968503937008" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600" verticalDpi="600"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="12.75" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="2" style="1" width="10.28125"/>
-    <col customWidth="1" min="3" max="3" style="1" width="16.28125"/>
-    <col min="4" max="4" style="1" width="10.28125"/>
-    <col customWidth="1" min="5" max="5" style="1" width="18.8515625"/>
-    <col min="6" max="16384" style="1" width="10.28125"/>
+    <col min="1" max="2" width="10.28" style="1"/>
+    <col min="3" max="3" width="16.28" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28" style="1"/>
+    <col min="5" max="5" width="18.8533333333333" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.28" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.5">
+    <row r="1" ht="15.75" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>45</v>
       </c>
@@ -1615,7 +1962,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" ht="114">
+    <row r="2" ht="91.5" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>49</v>
       </c>
@@ -1632,7 +1979,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" ht="99.75">
+    <row r="3" ht="78.75" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>54</v>
       </c>
@@ -1649,7 +1996,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" ht="71.25">
+    <row r="4" ht="60" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>58</v>
       </c>
@@ -1666,7 +2013,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" ht="71.25">
+    <row r="5" ht="63" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>62</v>
       </c>
@@ -1683,7 +2030,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" ht="57">
+    <row r="6" ht="47.25" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>67</v>
       </c>
@@ -1700,7 +2047,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" ht="57">
+    <row r="7" ht="47.25" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>71</v>
       </c>
@@ -1717,7 +2064,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" ht="71.25">
+    <row r="8" ht="63" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>75</v>
       </c>
@@ -1734,7 +2081,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" ht="71.25">
+    <row r="9" ht="60" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>80</v>
       </c>
@@ -1751,7 +2098,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" ht="71.25">
+    <row r="10" ht="47.25" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>84</v>
       </c>
@@ -1768,7 +2115,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" ht="57">
+    <row r="11" ht="47.25" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>88</v>
       </c>
@@ -1785,7 +2132,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" ht="57">
+    <row r="12" ht="47.25" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>93</v>
       </c>
@@ -1802,7 +2149,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" ht="57">
+    <row r="13" ht="44.25" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>96</v>
       </c>
@@ -1819,7 +2166,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="14" ht="71.25">
+    <row r="14" ht="63" spans="1:5">
       <c r="A14" s="1" t="s">
         <v>100</v>
       </c>
@@ -1836,7 +2183,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="15" ht="57">
+    <row r="15" ht="47.25" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>104</v>
       </c>
@@ -1853,7 +2200,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="16" ht="85.5">
+    <row r="16" ht="59.25" spans="1:5">
       <c r="A16" s="1" t="s">
         <v>108</v>
       </c>
@@ -1871,21 +2218,27 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageMargins left="0.700787401574803" right="0.700787401574803" top="0.751968503937008" bottom="0.751968503937008" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600" verticalDpi="600"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="12.75" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="16384" style="1" width="10.28125"/>
+    <col min="1" max="1" width="6.3" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.2" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.2" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.28" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42.75">
+    <row r="1" ht="31.5" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>112</v>
       </c>
@@ -1902,7 +2255,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" ht="71.25">
+    <row r="2" ht="60" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>117</v>
       </c>
@@ -1919,7 +2272,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" ht="85.5">
+    <row r="3" ht="59.25" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>122</v>
       </c>
@@ -1936,7 +2289,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" ht="71.25">
+    <row r="4" ht="63" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>126</v>
       </c>
@@ -1953,7 +2306,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" ht="57">
+    <row r="5" ht="47.25" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>129</v>
       </c>
@@ -1970,7 +2323,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" ht="57">
+    <row r="6" ht="47.25" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>132</v>
       </c>
@@ -1987,14 +2340,14 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" ht="71.25">
+    <row r="7" ht="60" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>135</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="5" t="s">
         <v>137</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -2004,7 +2357,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="8" ht="71.25">
+    <row r="8" ht="47.25" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>140</v>
       </c>
@@ -2021,14 +2374,14 @@
         <v>143</v>
       </c>
     </row>
-    <row r="9" ht="71.25">
+    <row r="9" ht="59.25" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>144</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="5" t="s">
         <v>137</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -2038,7 +2391,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="10" ht="57">
+    <row r="10" ht="43.5" spans="1:5">
       <c r="A10" s="1" t="s">
         <v>148</v>
       </c>
@@ -2055,7 +2408,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" ht="71.25">
+    <row r="11" ht="60" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>151</v>
       </c>
@@ -2073,166 +2426,167 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageMargins left="0.700787401574803" right="0.700787401574803" top="0.751968503937008" bottom="0.751968503937008" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600" verticalDpi="600"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="12.75" outlineLevelCol="1"/>
   <cols>
-    <col bestFit="1" min="1" max="1" style="3" width="4.28125"/>
+    <col min="1" max="1" width="4.28" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="2" ht="14.25">
-      <c r="A2" s="3">
+    <row r="2" spans="1:2">
+      <c r="A2" s="4">
         <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="3" ht="14.25">
-      <c r="A3" s="3">
-        <v>7.0999999999999996</v>
-      </c>
-      <c r="B3" s="5" t="s">
+    <row r="3" spans="1:2">
+      <c r="A3" s="4">
+        <v>7.1</v>
+      </c>
+      <c r="B3" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="4" ht="14.25">
-      <c r="A4" s="3">
-        <v>7.2000000000000002</v>
+    <row r="4" spans="1:2">
+      <c r="A4" s="4">
+        <v>7.2</v>
       </c>
       <c r="B4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="5" ht="14.25">
-      <c r="A5" s="3">
+    <row r="5" spans="1:2">
+      <c r="A5" s="4">
         <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="6" ht="14.25">
-      <c r="A6" s="3">
-        <v>8.0999999999999996</v>
+    <row r="6" spans="1:2">
+      <c r="A6" s="4">
+        <v>8.1</v>
       </c>
       <c r="B6" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="7" ht="14.25">
-      <c r="A7" s="3">
+    <row r="7" spans="1:2">
+      <c r="A7" s="4">
         <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="8" ht="14.25">
-      <c r="A8" s="3">
-        <v>9.0999999999999996</v>
+    <row r="8" spans="1:2">
+      <c r="A8" s="4">
+        <v>9.1</v>
       </c>
       <c r="B8" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="9" ht="14.25">
-      <c r="A9" s="3">
+    <row r="9" spans="1:2">
+      <c r="A9" s="4">
         <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="10" ht="14.25">
-      <c r="A10" s="3">
+    <row r="10" spans="1:2">
+      <c r="A10" s="4">
         <v>10.1</v>
       </c>
       <c r="B10" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="11" ht="14.25">
-      <c r="A11" s="3">
-        <v>10.199999999999999</v>
+    <row r="11" spans="1:2">
+      <c r="A11" s="4">
+        <v>10.2</v>
       </c>
       <c r="B11" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="12" ht="14.25">
-      <c r="A12" s="3">
+    <row r="12" spans="1:2">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="13" ht="14.25">
-      <c r="A13" s="3">
+    <row r="13" spans="1:2">
+      <c r="A13" s="4">
         <v>11.1</v>
       </c>
       <c r="B13" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="14" ht="14.25">
-      <c r="A14" s="3">
-        <v>11.199999999999999</v>
+    <row r="14" spans="1:2">
+      <c r="A14" s="4">
+        <v>11.2</v>
       </c>
       <c r="B14" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="15" ht="14.25">
-      <c r="A15" s="3">
-        <v>11.300000000000001</v>
+    <row r="15" spans="1:2">
+      <c r="A15" s="4">
+        <v>11.3</v>
       </c>
       <c r="B15" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="16" ht="14.25">
-      <c r="A16" s="3">
+    <row r="16" spans="1:2">
+      <c r="A16" s="4">
         <v>11.4</v>
       </c>
       <c r="B16" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="17" ht="14.25">
-      <c r="A17" s="3">
+    <row r="17" spans="1:2">
+      <c r="A17" s="4">
         <v>11.5</v>
       </c>
       <c r="B17" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="18" ht="14.25">
-      <c r="A18" s="3">
+    <row r="18" spans="1:2">
+      <c r="A18" s="4">
         <v>12</v>
       </c>
       <c r="B18" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="19" ht="14.25">
-      <c r="A19" s="3">
+    <row r="19" spans="1:2">
+      <c r="A19" s="4">
         <v>12.1</v>
       </c>
       <c r="B19" t="s">
@@ -2240,21 +2594,22 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageMargins left="0.700787401574803" right="0.700787401574803" top="0.751968503937008" bottom="0.751968503937008" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600" verticalDpi="600"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J61"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="16384" style="1" width="10.28125"/>
+    <col min="1" max="16384" width="10.28" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42.75">
+    <row r="1" ht="31.5" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>112</v>
       </c>
@@ -2283,7 +2638,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="2" ht="71.25">
+    <row r="2" ht="63" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>181</v>
       </c>
@@ -2299,8 +2654,8 @@
       <c r="E2" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="6">
-        <v>0.84999999999999998</v>
+      <c r="F2" s="3">
+        <v>0.85</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>186</v>
@@ -2315,7 +2670,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="3" ht="42.75">
+    <row r="3" ht="31.5" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>190</v>
       </c>
@@ -2331,7 +2686,7 @@
       <c r="E3" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="3">
         <v>0.62</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -2347,7 +2702,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="4" ht="42.75">
+    <row r="4" ht="31.5" spans="1:10">
       <c r="A4" s="1" t="s">
         <v>198</v>
       </c>
@@ -2363,8 +2718,8 @@
       <c r="E4" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F4" s="6">
-        <v>0.45000000000000001</v>
+      <c r="F4" s="3">
+        <v>0.45</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>202</v>
@@ -2379,7 +2734,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="5" ht="42.75">
+    <row r="5" ht="31.5" spans="1:10">
       <c r="A5" s="1" t="s">
         <v>206</v>
       </c>
@@ -2395,7 +2750,7 @@
       <c r="E5" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="3">
         <v>0.12</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -2411,7 +2766,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="6" ht="42.75">
+    <row r="6" ht="31.5" spans="1:10">
       <c r="A6" s="1" t="s">
         <v>213</v>
       </c>
@@ -2427,8 +2782,8 @@
       <c r="E6" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F6" s="6">
-        <v>0.34999999999999998</v>
+      <c r="F6" s="3">
+        <v>0.35</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>217</v>
@@ -2443,7 +2798,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="7" ht="42.75">
+    <row r="7" ht="47.25" spans="1:10">
       <c r="A7" s="1" t="s">
         <v>221</v>
       </c>
@@ -2459,8 +2814,8 @@
       <c r="E7" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F7" s="6">
-        <v>0.55000000000000004</v>
+      <c r="F7" s="3">
+        <v>0.55</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>225</v>
@@ -2475,7 +2830,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="8" ht="57">
+    <row r="8" ht="43.5" spans="1:10">
       <c r="A8" s="1" t="s">
         <v>229</v>
       </c>
@@ -2491,8 +2846,8 @@
       <c r="E8" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="F8" s="6">
-        <v>0.29999999999999999</v>
+      <c r="F8" s="3">
+        <v>0.3</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>233</v>
@@ -2507,242 +2862,241 @@
         <v>235</v>
       </c>
     </row>
-    <row r="10" ht="14.25">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:1">
+      <c r="A10" s="2" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="11" ht="14.25">
-      <c r="A11" s="7"/>
-    </row>
-    <row r="12" ht="14.25">
-      <c r="A12" s="7" t="s">
+    <row r="11" spans="1:1">
+      <c r="A11" s="2"/>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="2" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="13" ht="14.25">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:1">
+      <c r="A13" s="2" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="14" ht="14.25">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:1">
+      <c r="A14" s="2" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="15" ht="14.25">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:1">
+      <c r="A15" s="2" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="16" ht="14.25">
-      <c r="A16" s="7"/>
-    </row>
-    <row r="17" ht="14.25">
-      <c r="A17" s="7" t="s">
+    <row r="16" spans="1:1">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="2" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="18" ht="14.25">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:1">
+      <c r="A18" s="2" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="19" ht="14.25">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" s="2" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="20" ht="14.25">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:1">
+      <c r="A20" s="2" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="21" ht="14.25">
-      <c r="A21" s="7"/>
-    </row>
-    <row r="22" ht="14.25">
-      <c r="A22" s="7" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="2" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="23" ht="14.25">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:1">
+      <c r="A23" s="2" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="24" ht="14.25">
-      <c r="A24" s="7" t="s">
+    <row r="24" spans="1:1">
+      <c r="A24" s="2" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="25" ht="14.25">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:1">
+      <c r="A25" s="2" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="26" ht="14.25">
-      <c r="A26" s="7"/>
-    </row>
-    <row r="27" ht="14.25">
-      <c r="A27" s="7" t="s">
+    <row r="26" spans="1:1">
+      <c r="A26" s="2"/>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="2" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="28" ht="14.25">
-      <c r="A28" s="7"/>
-    </row>
-    <row r="29" ht="14.25">
-      <c r="A29" s="7" t="s">
+    <row r="28" spans="1:1">
+      <c r="A28" s="2"/>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="2" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="30" ht="14.25">
-      <c r="A30" s="7"/>
-    </row>
-    <row r="31" ht="14.25">
-      <c r="A31" s="7" t="s">
+    <row r="30" spans="1:1">
+      <c r="A30" s="2"/>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="2" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="32" ht="14.25">
-      <c r="A32" s="7"/>
-    </row>
-    <row r="33" ht="14.25">
-      <c r="A33" s="7" t="s">
+    <row r="32" spans="1:1">
+      <c r="A32" s="2"/>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="2" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="34" ht="14.25">
-      <c r="A34" s="7" t="s">
+    <row r="34" spans="1:1">
+      <c r="A34" s="2" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="35" ht="14.25">
-      <c r="A35" s="7" t="s">
+    <row r="35" spans="1:1">
+      <c r="A35" s="2" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="36" ht="14.25">
-      <c r="A36" s="7" t="s">
+    <row r="36" spans="1:1">
+      <c r="A36" s="2" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="37" ht="14.25">
-      <c r="A37" s="7" t="s">
+    <row r="37" spans="1:1">
+      <c r="A37" s="2" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="38" ht="14.25">
-      <c r="A38" s="7" t="s">
+    <row r="38" spans="1:1">
+      <c r="A38" s="2" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="39" ht="14.25">
-      <c r="A39" s="7" t="s">
+    <row r="39" spans="1:1">
+      <c r="A39" s="2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="40" ht="14.25">
-      <c r="A40" s="7" t="s">
+    <row r="40" spans="1:1">
+      <c r="A40" s="2" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="41" ht="14.25">
-      <c r="A41" s="7" t="s">
+    <row r="41" spans="1:1">
+      <c r="A41" s="2" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="42" ht="14.25">
-      <c r="A42" s="7"/>
-    </row>
-    <row r="43" ht="14.25">
-      <c r="A43" s="7" t="s">
+    <row r="42" spans="1:1">
+      <c r="A42" s="2"/>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="44" ht="14.25">
-      <c r="A44" s="7" t="s">
+    <row r="44" spans="1:1">
+      <c r="A44" s="2" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="45" ht="14.25">
-      <c r="A45" s="7" t="s">
+    <row r="45" spans="1:1">
+      <c r="A45" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="46" ht="14.25">
-      <c r="A46" s="7" t="s">
+    <row r="46" spans="1:1">
+      <c r="A46" s="2" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="47" ht="14.25">
-      <c r="A47" s="7" t="s">
+    <row r="47" spans="1:1">
+      <c r="A47" s="2" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="48" ht="14.25">
-      <c r="A48" s="7" t="s">
+    <row r="48" spans="1:1">
+      <c r="A48" s="2" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="49" ht="14.25">
-      <c r="A49" s="7"/>
-    </row>
-    <row r="50" ht="14.25">
-      <c r="A50" s="7" t="s">
+    <row r="49" spans="1:1">
+      <c r="A49" s="2"/>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="2" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="51" ht="14.25">
-      <c r="A51" s="7"/>
-    </row>
-    <row r="52" ht="14.25">
-      <c r="A52" s="7" t="s">
+    <row r="51" spans="1:1">
+      <c r="A51" s="2"/>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="2" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="53" ht="14.25">
-      <c r="A53" s="7"/>
-    </row>
-    <row r="54" ht="14.25">
-      <c r="A54" s="7" t="s">
+    <row r="53" spans="1:1">
+      <c r="A53" s="2"/>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="2" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="55" ht="14.25">
-      <c r="A55" s="7"/>
-    </row>
-    <row r="56" ht="14.25">
-      <c r="A56" s="7" t="s">
+    <row r="55" spans="1:1">
+      <c r="A55" s="2"/>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="2" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="57" ht="14.25">
-      <c r="A57" s="7" t="s">
+    <row r="57" spans="1:1">
+      <c r="A57" s="2" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="58" ht="14.25">
-      <c r="A58" s="7"/>
-    </row>
-    <row r="59" ht="14.25">
-      <c r="A59" s="7" t="s">
+    <row r="58" spans="1:1">
+      <c r="A58" s="2"/>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="2" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="60" ht="14.25">
-      <c r="A60" s="7"/>
-    </row>
-    <row r="61" ht="14.25">
-      <c r="A61" s="7" t="s">
+    <row r="60" spans="1:1">
+      <c r="A60" s="2"/>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="2" t="s">
         <v>271</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageMargins left="0.700787401574803" right="0.700787401574803" top="0.751968503937008" bottom="0.751968503937008" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600" verticalDpi="600"/>
   <headerFooter/>
 </worksheet>
 </file>